--- a/research/traditional_assets/database/data/kuwait/kuwait_steel.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_steel.xlsx
@@ -588,118 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.164</v>
+        <v>-0.135</v>
       </c>
       <c r="E2">
-        <v>-0.172</v>
+        <v>0.0007599999999999999</v>
       </c>
       <c r="G2">
-        <v>0.3512635379061372</v>
+        <v>0.03918367346938775</v>
       </c>
       <c r="H2">
-        <v>0.3512635379061372</v>
+        <v>0.03918367346938775</v>
       </c>
       <c r="I2">
-        <v>0.2605077712838799</v>
+        <v>-0.1507269110003419</v>
       </c>
       <c r="J2">
-        <v>0.2596345608773417</v>
+        <v>-0.1490702728794372</v>
       </c>
       <c r="K2">
-        <v>0.892</v>
+        <v>5.49</v>
       </c>
       <c r="L2">
-        <v>0.3220216606498195</v>
+        <v>2.240816326530612</v>
       </c>
       <c r="M2">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0199546485260771</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.973094170403587</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0199546485260771</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.973094170403587</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>1.28</v>
+        <v>7.6</v>
       </c>
       <c r="V2">
-        <v>0.0145124716553288</v>
+        <v>0.1095100864553314</v>
       </c>
       <c r="W2">
-        <v>0.01441033925686591</v>
+        <v>0.1190889370932755</v>
       </c>
       <c r="X2">
-        <v>0.06528563134337771</v>
+        <v>0.1132804678214539</v>
       </c>
       <c r="Y2">
-        <v>-0.0508752920865118</v>
+        <v>0.005808469271821617</v>
       </c>
       <c r="Z2">
-        <v>0.04727610497554576</v>
+        <v>0.05460655959798101</v>
       </c>
       <c r="AA2">
-        <v>0.01227451075531693</v>
+        <v>-0.008140214740278281</v>
       </c>
       <c r="AB2">
-        <v>0.06525421435082233</v>
+        <v>0.1132365389474962</v>
       </c>
       <c r="AC2">
-        <v>-0.0529797035955054</v>
+        <v>-0.1213767536877745</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.08196736771826349</v>
+        <v>0.04640465975418824</v>
       </c>
       <c r="AF2">
-        <v>0.08196736771826349</v>
+        <v>0.04640465975418824</v>
       </c>
       <c r="AG2">
-        <v>-1.198032632281737</v>
+        <v>-7.553595340245812</v>
       </c>
       <c r="AH2">
-        <v>0.0009284723728102619</v>
+        <v>0.0006682082388792234</v>
       </c>
       <c r="AI2">
-        <v>0.001774878213082789</v>
+        <v>0.0008177550636454587</v>
       </c>
       <c r="AJ2">
-        <v>-0.01377017863536568</v>
+        <v>-0.1221347527281764</v>
       </c>
       <c r="AK2">
-        <v>-0.02668107217821034</v>
+        <v>-0.1536957869561397</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.229</v>
+        <v>-5.91</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP2">
-        <v>-1.533972640565604</v>
+        <v>22.15130598312555</v>
       </c>
       <c r="AQ2">
-        <v>-2.851528384279476</v>
+        <v>0.06920473773265651</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kuwait Foundry Company - K.P.S.C. (KWSE:KFOUC)</t>
+          <t>Kuwait Foundry Company K.S.C.P. (KWSE:KFOUC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,118 +716,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.164</v>
+        <v>-0.135</v>
       </c>
       <c r="E3">
-        <v>-0.172</v>
+        <v>0.0007599999999999999</v>
       </c>
       <c r="G3">
-        <v>0.3512635379061372</v>
+        <v>0.03918367346938775</v>
       </c>
       <c r="H3">
-        <v>0.3512635379061372</v>
+        <v>0.03918367346938775</v>
       </c>
       <c r="I3">
-        <v>0.2605077712838799</v>
+        <v>-0.1507269110003419</v>
       </c>
       <c r="J3">
-        <v>0.2596345608773417</v>
+        <v>-0.1490702728794372</v>
       </c>
       <c r="K3">
-        <v>0.892</v>
+        <v>5.49</v>
       </c>
       <c r="L3">
-        <v>0.3220216606498195</v>
+        <v>2.240816326530612</v>
       </c>
       <c r="M3">
-        <v>1.76</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0199546485260771</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.973094170403587</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>1.76</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0199546485260771</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.973094170403587</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>1.28</v>
+        <v>7.6</v>
       </c>
       <c r="V3">
-        <v>0.0145124716553288</v>
+        <v>0.1095100864553314</v>
       </c>
       <c r="W3">
-        <v>0.01441033925686591</v>
+        <v>0.1190889370932755</v>
       </c>
       <c r="X3">
-        <v>0.06528563134337771</v>
+        <v>0.1132804678214539</v>
       </c>
       <c r="Y3">
-        <v>-0.0508752920865118</v>
+        <v>0.005808469271821617</v>
       </c>
       <c r="Z3">
-        <v>0.04727610497554576</v>
+        <v>0.05460655959798101</v>
       </c>
       <c r="AA3">
-        <v>0.01227451075531693</v>
+        <v>-0.008140214740278281</v>
       </c>
       <c r="AB3">
-        <v>0.06525421435082233</v>
+        <v>0.1132365389474962</v>
       </c>
       <c r="AC3">
-        <v>-0.0529797035955054</v>
+        <v>-0.1213767536877745</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.08196736771826349</v>
+        <v>0.04640465975418824</v>
       </c>
       <c r="AF3">
-        <v>0.08196736771826349</v>
+        <v>0.04640465975418824</v>
       </c>
       <c r="AG3">
-        <v>-1.198032632281737</v>
+        <v>-7.553595340245812</v>
       </c>
       <c r="AH3">
-        <v>0.0009284723728102619</v>
+        <v>0.0006682082388792234</v>
       </c>
       <c r="AI3">
-        <v>0.001774878213082789</v>
+        <v>0.0008177550636454587</v>
       </c>
       <c r="AJ3">
-        <v>-0.01377017863536568</v>
+        <v>-0.1221347527281764</v>
       </c>
       <c r="AK3">
-        <v>-0.02668107217821034</v>
+        <v>-0.1536957869561397</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.229</v>
+        <v>-5.91</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP3">
-        <v>-1.533972640565604</v>
+        <v>22.15130598312555</v>
       </c>
       <c r="AQ3">
-        <v>-2.851528384279476</v>
+        <v>0.06920473773265651</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_steel.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_steel.xlsx
@@ -588,115 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.135</v>
+        <v>-0.205</v>
       </c>
       <c r="E2">
-        <v>0.0007599999999999999</v>
+        <v>1.031</v>
       </c>
       <c r="G2">
-        <v>0.03918367346938775</v>
+        <v>-1.131221719457014</v>
       </c>
       <c r="H2">
-        <v>0.03918367346938775</v>
+        <v>-1.131221719457014</v>
       </c>
       <c r="I2">
-        <v>-0.1507269110003419</v>
+        <v>-1.389246502426248</v>
       </c>
       <c r="J2">
-        <v>-0.1490702728794372</v>
+        <v>-1.372815312829023</v>
       </c>
       <c r="K2">
-        <v>5.49</v>
+        <v>19.5</v>
       </c>
       <c r="L2">
-        <v>2.240816326530612</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>26.07</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.2982837528604119</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.336923076923077</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.2711670480549199</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.215384615384615</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.370000000000001</v>
+      </c>
+      <c r="T2">
+        <v>0.09090909090909094</v>
       </c>
       <c r="U2">
-        <v>7.6</v>
+        <v>3.33</v>
       </c>
       <c r="V2">
-        <v>0.1095100864553314</v>
+        <v>0.03810068649885583</v>
       </c>
       <c r="W2">
-        <v>0.1190889370932755</v>
+        <v>0.3439153439153439</v>
       </c>
       <c r="X2">
-        <v>0.1132804678214539</v>
+        <v>0.09410076890619451</v>
       </c>
       <c r="Y2">
-        <v>0.005808469271821617</v>
+        <v>0.2498145750091494</v>
       </c>
       <c r="Z2">
-        <v>0.05460655959798101</v>
+        <v>0.04496789529666726</v>
       </c>
       <c r="AA2">
-        <v>-0.008140214740278281</v>
+        <v>-0.06173261524895703</v>
       </c>
       <c r="AB2">
-        <v>0.1132365389474962</v>
+        <v>0.09407855216517955</v>
       </c>
       <c r="AC2">
-        <v>-0.1213767536877745</v>
+        <v>-0.1558111674141366</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.04640465975418824</v>
+        <v>0.0461738518100353</v>
       </c>
       <c r="AF2">
-        <v>0.04640465975418824</v>
+        <v>0.0461738518100353</v>
       </c>
       <c r="AG2">
-        <v>-7.553595340245812</v>
+        <v>-3.283826148189965</v>
       </c>
       <c r="AH2">
-        <v>0.0006682082388792234</v>
+        <v>0.0005280259818832491</v>
       </c>
       <c r="AI2">
-        <v>0.0008177550636454587</v>
+        <v>0.001095564498271823</v>
       </c>
       <c r="AJ2">
-        <v>-0.1221347527281764</v>
+        <v>-0.03903917638925396</v>
       </c>
       <c r="AK2">
-        <v>-0.1536957869561397</v>
+        <v>-0.08459942911237854</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-5.91</v>
+        <v>-23.1</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
       <c r="AP2">
-        <v>22.15130598312555</v>
+        <v>1.076311421891172</v>
       </c>
       <c r="AQ2">
-        <v>0.06920473773265651</v>
+        <v>0.1346320346320346</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.135</v>
+        <v>-0.205</v>
       </c>
       <c r="E3">
-        <v>0.0007599999999999999</v>
+        <v>1.031</v>
       </c>
       <c r="G3">
-        <v>0.03918367346938775</v>
+        <v>-1.131221719457014</v>
       </c>
       <c r="H3">
-        <v>0.03918367346938775</v>
+        <v>-1.131221719457014</v>
       </c>
       <c r="I3">
-        <v>-0.1507269110003419</v>
+        <v>-1.389246502426248</v>
       </c>
       <c r="J3">
-        <v>-0.1490702728794372</v>
+        <v>-1.372815312829023</v>
       </c>
       <c r="K3">
-        <v>5.49</v>
+        <v>19.5</v>
       </c>
       <c r="L3">
-        <v>2.240816326530612</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>26.07</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.2982837528604119</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>1.336923076923077</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>23.7</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.2711670480549199</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>1.215384615384615</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.370000000000001</v>
+      </c>
+      <c r="T3">
+        <v>0.09090909090909094</v>
       </c>
       <c r="U3">
-        <v>7.6</v>
+        <v>3.33</v>
       </c>
       <c r="V3">
-        <v>0.1095100864553314</v>
+        <v>0.03810068649885583</v>
       </c>
       <c r="W3">
-        <v>0.1190889370932755</v>
+        <v>0.3439153439153439</v>
       </c>
       <c r="X3">
-        <v>0.1132804678214539</v>
+        <v>0.09410076890619451</v>
       </c>
       <c r="Y3">
-        <v>0.005808469271821617</v>
+        <v>0.2498145750091494</v>
       </c>
       <c r="Z3">
-        <v>0.05460655959798101</v>
+        <v>0.04496789529666726</v>
       </c>
       <c r="AA3">
-        <v>-0.008140214740278281</v>
+        <v>-0.06173261524895703</v>
       </c>
       <c r="AB3">
-        <v>0.1132365389474962</v>
+        <v>0.09407855216517955</v>
       </c>
       <c r="AC3">
-        <v>-0.1213767536877745</v>
+        <v>-0.1558111674141366</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.04640465975418824</v>
+        <v>0.0461738518100353</v>
       </c>
       <c r="AF3">
-        <v>0.04640465975418824</v>
+        <v>0.0461738518100353</v>
       </c>
       <c r="AG3">
-        <v>-7.553595340245812</v>
+        <v>-3.283826148189965</v>
       </c>
       <c r="AH3">
-        <v>0.0006682082388792234</v>
+        <v>0.0005280259818832491</v>
       </c>
       <c r="AI3">
-        <v>0.0008177550636454587</v>
+        <v>0.001095564498271823</v>
       </c>
       <c r="AJ3">
-        <v>-0.1221347527281764</v>
+        <v>-0.03903917638925396</v>
       </c>
       <c r="AK3">
-        <v>-0.1536957869561397</v>
+        <v>-0.08459942911237854</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-5.91</v>
+        <v>-23.1</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AP3">
-        <v>22.15130598312555</v>
+        <v>1.076311421891172</v>
       </c>
       <c r="AQ3">
-        <v>0.06920473773265651</v>
+        <v>0.1346320346320346</v>
       </c>
     </row>
   </sheetData>
